--- a/data/trans_orig/Q23_tabaco-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media de inicio en el consumo de tabaco</t>
+          <t>Edad media de inicio en el consumo de tabaco (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 17,0</t>
+          <t>16,41; 17,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,84</t>
+          <t>16,89; 17,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,96</t>
+          <t>17,04; 17,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 19,19</t>
+          <t>17,33; 19,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 18,98</t>
+          <t>17,44; 19,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,75; 17,8</t>
+          <t>16,74; 17,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,76; 19,13</t>
+          <t>17,76; 19,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,51</t>
+          <t>16,83; 17,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,24; 18,15</t>
+          <t>17,21; 18,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,57</t>
+          <t>16,82; 17,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,18</t>
+          <t>17,47; 18,18</t>
         </is>
       </c>
     </row>
@@ -856,57 +856,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 17,26</t>
+          <t>16,3; 17,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 17,25</t>
+          <t>16,48; 17,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,17; 17,38</t>
+          <t>16,18; 17,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,62</t>
+          <t>16,65; 17,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,5</t>
+          <t>16,66; 17,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,79</t>
+          <t>16,79; 17,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 18,23</t>
+          <t>16,98; 18,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,73</t>
+          <t>16,87; 17,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,23</t>
+          <t>16,56; 17,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 17,31</t>
+          <t>16,71; 17,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,62</t>
+          <t>16,7; 17,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 17,16</t>
+          <t>16,19; 17,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 16,93</t>
+          <t>16,15; 16,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,0; 16,93</t>
+          <t>16,05; 16,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 16,47</t>
+          <t>15,84; 16,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 20,53</t>
+          <t>17,37; 20,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,54; 19,42</t>
+          <t>17,5; 19,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,86; 21,68</t>
+          <t>17,91; 21,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,76</t>
+          <t>16,38; 17,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,41</t>
+          <t>16,5; 17,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,28</t>
+          <t>16,58; 17,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 17,5</t>
+          <t>16,47; 17,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 16,56</t>
+          <t>15,93; 16,54</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,04; 16,48</t>
+          <t>16,02; 16,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 16,45</t>
+          <t>16,0; 16,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,18; 16,69</t>
+          <t>16,15; 16,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 16,79</t>
+          <t>16,27; 16,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,66</t>
+          <t>16,8; 17,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,15</t>
+          <t>17,03; 18,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 18,12</t>
+          <t>17,23; 18,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,67</t>
+          <t>16,87; 17,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,71</t>
+          <t>16,3; 16,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 16,89</t>
+          <t>16,39; 16,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,14</t>
+          <t>16,64; 17,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 16,99</t>
+          <t>16,54; 17,0</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 16,48</t>
+          <t>15,69; 16,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,02; 16,9</t>
+          <t>16,0; 16,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,98; 16,82</t>
+          <t>15,94; 16,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 17,21</t>
+          <t>15,96; 17,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,72</t>
+          <t>17,04; 18,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,14</t>
+          <t>16,97; 18,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,86; 18,05</t>
+          <t>16,82; 17,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,09; 17,84</t>
+          <t>17,04; 17,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,38</t>
+          <t>16,42; 17,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,3</t>
+          <t>16,6; 17,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 17,19</t>
+          <t>16,48; 17,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,32</t>
+          <t>16,57; 17,32</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,41; 16,87</t>
+          <t>15,4; 16,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,45; 16,71</t>
+          <t>15,42; 16,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,39; 16,34</t>
+          <t>15,38; 16,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,37; 17,64</t>
+          <t>15,46; 17,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,07; 18,27</t>
+          <t>17,09; 18,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 19,27</t>
+          <t>17,46; 19,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,47; 19,09</t>
+          <t>17,5; 19,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 18,85</t>
+          <t>17,15; 18,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,72; 17,73</t>
+          <t>16,72; 17,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 18,6</t>
+          <t>17,13; 18,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,04; 18,21</t>
+          <t>17,01; 18,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,93; 18,25</t>
+          <t>16,89; 18,19</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,23; 16,54</t>
+          <t>16,23; 16,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,52 +1566,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,7</t>
+          <t>16,33; 16,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,78</t>
+          <t>16,33; 16,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,8</t>
+          <t>17,25; 17,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,44; 18,01</t>
+          <t>17,41; 17,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,96</t>
+          <t>17,43; 17,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,69</t>
+          <t>17,29; 17,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,94</t>
+          <t>16,65; 16,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,12</t>
+          <t>16,84; 17,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,15</t>
+          <t>16,84; 17,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,07</t>
+          <t>16,64; 17,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,47</t>
+          <t>17,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,32</t>
+          <t>18,29</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,81</t>
+          <t>17,84</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 17,03</t>
+          <t>16,41; 17,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,89; 17,86</t>
+          <t>16,96; 17,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,69</t>
+          <t>16,67; 17,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,91</t>
+          <t>17,15; 18,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 19,1</t>
+          <t>17,38; 19,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 19,34</t>
+          <t>17,39; 19,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,75</t>
+          <t>16,71; 17,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,76; 19,05</t>
+          <t>17,73; 19,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,51</t>
+          <t>16,8; 17,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,21; 18,1</t>
+          <t>17,25; 18,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,55</t>
+          <t>16,82; 17,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 18,18</t>
+          <t>17,5; 18,26</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,11</t>
+          <t>17,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,26</t>
+          <t>17,32</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,18</t>
+          <t>17,22</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 17,21</t>
+          <t>16,32; 17,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,24</t>
+          <t>16,43; 17,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 17,42</t>
+          <t>16,18; 17,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,61</t>
+          <t>16,75; 17,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,47</t>
+          <t>16,67; 17,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,79</t>
+          <t>16,82; 17,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 18,22</t>
+          <t>16,96; 18,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,69</t>
+          <t>16,91; 17,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,22</t>
+          <t>16,58; 17,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,31</t>
+          <t>16,73; 17,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 17,59</t>
+          <t>16,67; 17,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,86; 17,54</t>
+          <t>16,93; 17,52</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>16,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,19</t>
+          <t>16,48</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,19; 17,2</t>
+          <t>16,2; 17,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,9</t>
+          <t>16,18; 16,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,05; 16,93</t>
+          <t>15,99; 16,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 16,46</t>
+          <t>15,97; 16,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 20,46</t>
+          <t>17,31; 20,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,5; 19,41</t>
+          <t>17,53; 19,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 21,55</t>
+          <t>17,89; 21,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 17,86</t>
+          <t>16,39; 17,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,5; 17,41</t>
+          <t>16,48; 17,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,58; 17,25</t>
+          <t>16,55; 17,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,44</t>
+          <t>16,5; 17,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,54</t>
+          <t>16,11; 16,93</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>16,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,21</t>
+          <t>17,33</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,75</t>
+          <t>16,8</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,0; 16,45</t>
+          <t>15,99; 16,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,72</t>
+          <t>16,19; 16,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,27; 16,8</t>
+          <t>16,28; 16,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,65</t>
+          <t>16,75; 17,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,03; 18,21</t>
+          <t>17,05; 18,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 18,1</t>
+          <t>17,22; 18,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,72</t>
+          <t>17,0; 17,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,72</t>
+          <t>16,28; 16,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 16,87</t>
+          <t>16,4; 16,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,14</t>
+          <t>16,68; 17,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 17,0</t>
+          <t>16,61; 17,04</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,45</t>
+          <t>16,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,41</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,91</t>
+          <t>16,93</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 16,58</t>
+          <t>15,71; 16,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,0; 16,92</t>
+          <t>16,03; 16,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,94; 16,82</t>
+          <t>15,96; 16,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,96; 17,13</t>
+          <t>16,0; 17,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,04; 18,9</t>
+          <t>17,11; 18,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 18,17</t>
+          <t>17,0; 18,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,89</t>
+          <t>16,83; 18,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,81</t>
+          <t>17,16; 17,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 17,35</t>
+          <t>16,43; 17,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,3</t>
+          <t>16,62; 17,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,22</t>
+          <t>16,46; 17,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,32</t>
+          <t>16,65; 17,28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,35</t>
+          <t>16,36</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>17,76</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,43</t>
+          <t>17,48</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,4; 16,85</t>
+          <t>15,41; 16,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 16,69</t>
+          <t>15,4; 16,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 16,33</t>
+          <t>15,37; 16,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,46; 17,66</t>
+          <t>15,55; 17,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,09; 18,35</t>
+          <t>17,15; 18,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 19,24</t>
+          <t>17,41; 19,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 19,2</t>
+          <t>17,48; 19,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,15; 18,67</t>
+          <t>17,22; 18,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,72; 17,77</t>
+          <t>16,75; 17,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,13; 18,62</t>
+          <t>17,16; 18,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,01; 18,19</t>
+          <t>16,99; 18,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,19</t>
+          <t>16,99; 18,31</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,57</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,48</t>
+          <t>17,54</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>17,04</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,23; 16,52</t>
+          <t>16,22; 16,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,65</t>
+          <t>16,35; 16,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,7</t>
+          <t>16,31; 16,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,77</t>
+          <t>16,54; 16,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,83</t>
+          <t>17,24; 17,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,41; 17,99</t>
+          <t>17,45; 18,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,95</t>
+          <t>17,41; 17,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,29; 17,71</t>
+          <t>17,35; 17,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,93</t>
+          <t>16,66; 16,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,13</t>
+          <t>16,83; 17,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,12</t>
+          <t>16,83; 17,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,06</t>
+          <t>16,9; 17,18</t>
         </is>
       </c>
     </row>
